--- a/www/terminologies/ValueSet-JDV-J183-Diplome-EPARS.xlsx
+++ b/www/terminologies/ValueSet-JDV-J183-Diplome-EPARS.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -324,13 +324,13 @@
     <t>DIP356</t>
   </si>
   <si>
-    <t>Licence + Maîtrise + DESS en psychologie</t>
+    <t>Licence psychologie + Maîtrise psychologie + DESS en psychologie</t>
   </si>
   <si>
     <t>DIP357</t>
   </si>
   <si>
-    <t>Licence + Maîtrise + diplôme annexe Décret 90-255</t>
+    <t>Licence psychologie + Maîtrise psychologie + diplôme annexe Décret 90-255</t>
   </si>
   <si>
     <t>DIP358</t>

--- a/www/terminologies/ValueSet-JDV-J183-Diplome-EPARS.xlsx
+++ b/www/terminologies/ValueSet-JDV-J183-Diplome-EPARS.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -162,7 +162,7 @@
     <t>DIP322</t>
   </si>
   <si>
-    <t>Master en Psychologie ou Psychanalyse</t>
+    <t>Master en Psychologie ou Psychanalyse + formation établissement agréé incluant un stage en ESSMS</t>
   </si>
   <si>
     <t>DIP323</t>
